--- a/results/tables/tableA2_media_type_placebo.xlsx
+++ b/results/tables/tableA2_media_type_placebo.xlsx
@@ -233,16 +233,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -258,7 +250,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -266,30 +258,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -588,61 +562,61 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:19">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -657,22 +631,22 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>0.0842931125485394</v>
+        <v>0.0842931125485393</v>
       </c>
       <c r="E2">
-        <v>0.0399627426453581</v>
+        <v>0.0399627426453814</v>
       </c>
       <c r="F2">
-        <v>0.0350401845896148</v>
+        <v>0.0350401845897212</v>
       </c>
       <c r="G2" t="s">
         <v>48</v>
       </c>
       <c r="H2">
-        <v>0.0185602503653938</v>
+        <v>0.0185602503653554</v>
       </c>
       <c r="I2">
-        <v>0.150025974731685</v>
+        <v>0.1500259747317233</v>
       </c>
       <c r="J2">
         <v>0.9</v>
@@ -713,19 +687,19 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>-0.0190976254913111</v>
+        <v>0.0318995534718272</v>
       </c>
       <c r="E3">
-        <v>0.0324037429830594</v>
+        <v>0.0239299082577323</v>
       </c>
       <c r="F3">
-        <v>0.5556814635846445</v>
+        <v>0.182666263746118</v>
       </c>
       <c r="H3">
-        <v>-0.0723970396637998</v>
+        <v>-0.0074616429185198</v>
       </c>
       <c r="I3">
-        <v>0.0342017886811775</v>
+        <v>0.0712607498621743</v>
       </c>
       <c r="J3">
         <v>0.9</v>
@@ -769,19 +743,19 @@
         <v>0.2011236993794083</v>
       </c>
       <c r="E4">
-        <v>0.07866718700040951</v>
+        <v>0.0786671870003106</v>
       </c>
       <c r="F4">
-        <v>0.0106402549524429</v>
+        <v>0.0106402549523447</v>
       </c>
       <c r="G4" t="s">
         <v>48</v>
       </c>
       <c r="H4">
-        <v>0.071727691519715</v>
+        <v>0.07172769151987771</v>
       </c>
       <c r="I4">
-        <v>0.3305197072391017</v>
+        <v>0.3305197072389388</v>
       </c>
       <c r="J4">
         <v>0.9</v>
@@ -822,19 +796,19 @@
         <v>37</v>
       </c>
       <c r="D5">
-        <v>-0.0038432561278597</v>
+        <v>0.0382743187697822</v>
       </c>
       <c r="E5">
-        <v>0.0624237285752256</v>
+        <v>0.0476145719195806</v>
       </c>
       <c r="F5">
-        <v>0.9509134689344072</v>
+        <v>0.4215846610455653</v>
       </c>
       <c r="H5">
-        <v>-0.1065211524826539</v>
+        <v>-0.0400446825478817</v>
       </c>
       <c r="I5">
-        <v>0.09883464022693431</v>
+        <v>0.1165933200874463</v>
       </c>
       <c r="J5">
         <v>0.9</v>
@@ -878,19 +852,19 @@
         <v>0.2031202350300649</v>
       </c>
       <c r="E6">
-        <v>0.0911356848922768</v>
+        <v>0.0911356848922763</v>
       </c>
       <c r="F6">
-        <v>0.0259451075622656</v>
+        <v>0.0259451075622649</v>
       </c>
       <c r="G6" t="s">
         <v>48</v>
       </c>
       <c r="H6">
-        <v>0.0532153731902968</v>
+        <v>0.0532153731902977</v>
       </c>
       <c r="I6">
-        <v>0.3530250968698329</v>
+        <v>0.3530250968698322</v>
       </c>
       <c r="J6">
         <v>0.9</v>
@@ -931,19 +905,19 @@
         <v>39</v>
       </c>
       <c r="D7">
-        <v>-0.029859940861782</v>
+        <v>0.034172700909818</v>
       </c>
       <c r="E7">
-        <v>0.07100739481419931</v>
+        <v>0.0591430903437533</v>
       </c>
       <c r="F7">
-        <v>0.6741537425278228</v>
+        <v>0.5634691379184456</v>
       </c>
       <c r="H7">
-        <v>-0.146656711762293</v>
+        <v>-0.0631090257512233</v>
       </c>
       <c r="I7">
-        <v>0.0869368300387289</v>
+        <v>0.1314544275708593</v>
       </c>
       <c r="J7">
         <v>0.9</v>
@@ -987,19 +961,19 @@
         <v>0.2072364021401371</v>
       </c>
       <c r="E8">
-        <v>0.1162719669889471</v>
+        <v>0.1162719669886714</v>
       </c>
       <c r="F8">
-        <v>0.0748785547150614</v>
+        <v>0.0748785547143722</v>
       </c>
       <c r="G8" t="s">
         <v>49</v>
       </c>
       <c r="H8">
-        <v>0.0159860355255856</v>
+        <v>0.0159860355260391</v>
       </c>
       <c r="I8">
-        <v>0.3984867687546886</v>
+        <v>0.3984867687542351</v>
       </c>
       <c r="J8">
         <v>0.9</v>
@@ -1040,19 +1014,19 @@
         <v>41</v>
       </c>
       <c r="D9">
-        <v>0.032201998602147</v>
+        <v>0.0564664958691171</v>
       </c>
       <c r="E9">
-        <v>0.08178334966884961</v>
+        <v>0.0769850133595632</v>
       </c>
       <c r="F9">
-        <v>0.6938186027261692</v>
+        <v>0.4633743549062654</v>
       </c>
       <c r="H9">
-        <v>-0.1023196407249008</v>
+        <v>-0.0701625825762679</v>
       </c>
       <c r="I9">
-        <v>0.1667236379291949</v>
+        <v>0.1830955743145023</v>
       </c>
       <c r="J9">
         <v>0.9</v>
@@ -1093,22 +1067,22 @@
         <v>42</v>
       </c>
       <c r="D10">
-        <v>0.2154708583914853</v>
+        <v>0.2154708583914855</v>
       </c>
       <c r="E10">
-        <v>0.0889473323335338</v>
+        <v>0.0889473323335303</v>
       </c>
       <c r="F10">
-        <v>0.0155021492672648</v>
+        <v>0.0155021492672606</v>
       </c>
       <c r="G10" t="s">
         <v>48</v>
       </c>
       <c r="H10">
-        <v>0.0691655161950141</v>
+        <v>0.0691655161950202</v>
       </c>
       <c r="I10">
-        <v>0.3617762005879565</v>
+        <v>0.3617762005879508</v>
       </c>
       <c r="J10">
         <v>0.9</v>
@@ -1149,19 +1123,19 @@
         <v>43</v>
       </c>
       <c r="D11">
-        <v>-0.0345898846934828</v>
+        <v>-0.0850487429787847</v>
       </c>
       <c r="E11">
-        <v>0.1096230748972723</v>
+        <v>0.1336398123354226</v>
       </c>
       <c r="F11">
-        <v>0.7523877908249088</v>
+        <v>0.5245849332801513</v>
       </c>
       <c r="H11">
-        <v>-0.2149037970358342</v>
+        <v>-0.3048666730038187</v>
       </c>
       <c r="I11">
-        <v>0.1457240276488685</v>
+        <v>0.1347691870462492</v>
       </c>
       <c r="J11">
         <v>0.9</v>
@@ -1205,7 +1179,7 @@
         <v>0.2285087916131138</v>
       </c>
       <c r="E12">
-        <v>0.0860154538338445</v>
+        <v>0.0860154538338444</v>
       </c>
       <c r="F12">
         <v>0.007954422130128201</v>
@@ -1214,10 +1188,10 @@
         <v>50</v>
       </c>
       <c r="H12">
-        <v>0.0870259604006377</v>
+        <v>0.0870259604006379</v>
       </c>
       <c r="I12">
-        <v>0.3699916228255899</v>
+        <v>0.3699916228255898</v>
       </c>
       <c r="J12">
         <v>0.9</v>
@@ -1258,19 +1232,19 @@
         <v>45</v>
       </c>
       <c r="D13">
-        <v>-0.0042185489212171</v>
+        <v>0.09130623975805589</v>
       </c>
       <c r="E13">
-        <v>0.1049666611514509</v>
+        <v>0.1224377836656256</v>
       </c>
       <c r="F13">
-        <v>0.9679460244385432</v>
+        <v>0.4559124365996427</v>
       </c>
       <c r="H13">
-        <v>-0.1768733422251674</v>
+        <v>-0.1100859927802482</v>
       </c>
       <c r="I13">
-        <v>0.1684362443827332</v>
+        <v>0.29269847229636</v>
       </c>
       <c r="J13">
         <v>0.9</v>
@@ -1314,19 +1288,19 @@
         <v>0.2019054059065828</v>
       </c>
       <c r="E14">
-        <v>0.1002677955064572</v>
+        <v>0.1002677955064552</v>
       </c>
       <c r="F14">
-        <v>0.0441753969838323</v>
+        <v>0.0441753969838283</v>
       </c>
       <c r="G14" t="s">
         <v>48</v>
       </c>
       <c r="H14">
-        <v>0.0369795588013582</v>
+        <v>0.0369795588013613</v>
       </c>
       <c r="I14">
-        <v>0.3668312530118075</v>
+        <v>0.3668312530118043</v>
       </c>
       <c r="J14">
         <v>0.9</v>
@@ -1367,19 +1341,19 @@
         <v>47</v>
       </c>
       <c r="D15">
-        <v>-0.0297064632032413</v>
+        <v>-0.0943181043156498</v>
       </c>
       <c r="E15">
-        <v>0.1117160999719117</v>
+        <v>0.1270450668405377</v>
       </c>
       <c r="F15">
-        <v>0.7903349949634599</v>
+        <v>0.4579307216164767</v>
       </c>
       <c r="H15">
-        <v>-0.2134630954309136</v>
+        <v>-0.3032886432946006</v>
       </c>
       <c r="I15">
-        <v>0.154050169024431</v>
+        <v>0.1146524346633008</v>
       </c>
       <c r="J15">
         <v>0.9</v>

--- a/results/tables/tableA2_media_type_placebo.xlsx
+++ b/results/tables/tableA2_media_type_placebo.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="85">
   <si>
     <t>specification_id</t>
   </si>
@@ -76,42 +76,63 @@
     <t>placebo_nondevrel_m1_13_devrel</t>
   </si>
   <si>
+    <t>placebo_nondevrel_m1_13_allnews</t>
+  </si>
+  <si>
     <t>placebo_nondevrel_m1_13_generic</t>
   </si>
   <si>
     <t>placebo_nondevrel_roll24_devrel</t>
   </si>
   <si>
+    <t>placebo_nondevrel_roll24_allnews</t>
+  </si>
+  <si>
     <t>placebo_nondevrel_roll24_generic</t>
   </si>
   <si>
     <t>placebo_nondevrel_roll36_devrel</t>
   </si>
   <si>
+    <t>placebo_nondevrel_roll36_allnews</t>
+  </si>
+  <si>
     <t>placebo_nondevrel_roll36_generic</t>
   </si>
   <si>
     <t>placebo_nondevrel_roll60_devrel</t>
   </si>
   <si>
+    <t>placebo_nondevrel_roll60_allnews</t>
+  </si>
+  <si>
     <t>placebo_nondevrel_roll60_generic</t>
   </si>
   <si>
     <t>placebo_nondevrel_streak24_devrel</t>
   </si>
   <si>
+    <t>placebo_nondevrel_streak24_allnews</t>
+  </si>
+  <si>
     <t>placebo_nondevrel_streak24_generic</t>
   </si>
   <si>
     <t>placebo_nondevrel_streak36_devrel</t>
   </si>
   <si>
+    <t>placebo_nondevrel_streak36_allnews</t>
+  </si>
+  <si>
     <t>placebo_nondevrel_streak36_generic</t>
   </si>
   <si>
     <t>placebo_nondevrel_streak60_devrel</t>
   </si>
   <si>
+    <t>placebo_nondevrel_streak60_allnews</t>
+  </si>
+  <si>
     <t>placebo_nondevrel_streak60_generic</t>
   </si>
   <si>
@@ -121,43 +142,64 @@
     <t>devrel_media_m1_13</t>
   </si>
   <si>
-    <t>nondevrel_m1_13</t>
+    <t>allnews_m1_13</t>
+  </si>
+  <si>
+    <t>generic_m1_13</t>
   </si>
   <si>
     <t>devrel_media_roll24</t>
   </si>
   <si>
-    <t>nondevrel_roll24</t>
+    <t>allnews_roll24</t>
+  </si>
+  <si>
+    <t>generic_roll24</t>
   </si>
   <si>
     <t>devrel_media_roll36</t>
   </si>
   <si>
-    <t>nondevrel_roll36</t>
+    <t>allnews_roll36</t>
+  </si>
+  <si>
+    <t>generic_roll36</t>
   </si>
   <si>
     <t>devrel_media_roll60</t>
   </si>
   <si>
-    <t>nondevrel_roll60</t>
+    <t>allnews_roll60</t>
+  </si>
+  <si>
+    <t>generic_roll60</t>
   </si>
   <si>
     <t>_devrel_streak24</t>
   </si>
   <si>
-    <t>_nondevrel_streak24</t>
+    <t>_allnews_streak24</t>
+  </si>
+  <si>
+    <t>_generic_streak24</t>
   </si>
   <si>
     <t>_devrel_streak36</t>
   </si>
   <si>
-    <t>_nondevrel_streak36</t>
+    <t>_allnews_streak36</t>
+  </si>
+  <si>
+    <t>_generic_streak36</t>
   </si>
   <si>
     <t>_devrel_streak60</t>
   </si>
   <si>
-    <t>_nondevrel_streak60</t>
+    <t>_allnews_streak60</t>
+  </si>
+  <si>
+    <t>_generic_streak60</t>
   </si>
   <si>
     <t>*</t>
@@ -178,25 +220,25 @@
     <t>ln_gdppc;ln_population;log_bilateral_trade;ln_conflict_deaths;ln_disaster_affected</t>
   </si>
   <si>
-    <t>Devrel-ODA panel, matched sample (dropna on both devrel and generic m1_13 regressors + controls)</t>
-  </si>
-  <si>
-    <t>Devrel-ODA panel, matched sample (dropna on both devrel and generic roll24 regressors + controls)</t>
-  </si>
-  <si>
-    <t>Devrel-ODA panel, matched sample (dropna on both devrel and generic roll36 regressors + controls)</t>
-  </si>
-  <si>
-    <t>Devrel-ODA panel, matched sample (dropna on both devrel and generic roll60 regressors + controls)</t>
-  </si>
-  <si>
-    <t>Devrel-ODA panel, matched sample (dropna on both devrel and generic streak24 regressors + controls)</t>
-  </si>
-  <si>
-    <t>Devrel-ODA panel, matched sample (dropna on both devrel and generic streak36 regressors + controls)</t>
-  </si>
-  <si>
-    <t>Devrel-ODA panel, matched sample (dropna on both devrel and generic streak60 regressors + controls)</t>
+    <t>Devrel-ODA panel, matched sample (dropna on the devrel, all-news and sports m1_13 regressors + controls)</t>
+  </si>
+  <si>
+    <t>Devrel-ODA panel, matched sample (dropna on the devrel, all-news and sports roll24 regressors + controls)</t>
+  </si>
+  <si>
+    <t>Devrel-ODA panel, matched sample (dropna on the devrel, all-news and sports roll36 regressors + controls)</t>
+  </si>
+  <si>
+    <t>Devrel-ODA panel, matched sample (dropna on the devrel, all-news and sports roll60 regressors + controls)</t>
+  </si>
+  <si>
+    <t>Devrel-ODA panel, matched sample (dropna on the devrel, all-news and sports streak24 regressors + controls)</t>
+  </si>
+  <si>
+    <t>Devrel-ODA panel, matched sample (dropna on the devrel, all-news and sports streak36 regressors + controls)</t>
+  </si>
+  <si>
+    <t>Devrel-ODA panel, matched sample (dropna on the devrel, all-news and sports streak60 regressors + controls)</t>
   </si>
   <si>
     <t>2-13 months pre-allocation</t>
@@ -558,7 +600,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:S22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:19">
@@ -625,10 +667,10 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D2">
         <v>0.0842931125485393</v>
@@ -640,7 +682,7 @@
         <v>0.0350401845897212</v>
       </c>
       <c r="G2" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="H2">
         <v>0.0185602503653554</v>
@@ -658,22 +700,22 @@
         <v>141</v>
       </c>
       <c r="N2" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="O2" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="P2" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="Q2" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="R2" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="S2" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -681,25 +723,25 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D3">
-        <v>0.0318995534718272</v>
+        <v>0.07291344900955481</v>
       </c>
       <c r="E3">
-        <v>0.0239299082577323</v>
+        <v>0.0452807770095042</v>
       </c>
       <c r="F3">
-        <v>0.182666263746118</v>
+        <v>0.1074967207630575</v>
       </c>
       <c r="H3">
-        <v>-0.0074616429185198</v>
+        <v>-0.0015668012857091</v>
       </c>
       <c r="I3">
-        <v>0.0712607498621743</v>
+        <v>0.1473936993048188</v>
       </c>
       <c r="J3">
         <v>0.9</v>
@@ -711,22 +753,22 @@
         <v>141</v>
       </c>
       <c r="N3" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="O3" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="P3" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="Q3" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="R3" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="S3" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -734,28 +776,25 @@
         <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D4">
-        <v>0.2011236993794083</v>
+        <v>0.0318995534718272</v>
       </c>
       <c r="E4">
-        <v>0.0786671870003106</v>
+        <v>0.0239299082577323</v>
       </c>
       <c r="F4">
-        <v>0.0106402549523447</v>
-      </c>
-      <c r="G4" t="s">
-        <v>48</v>
+        <v>0.182666263746118</v>
       </c>
       <c r="H4">
-        <v>0.07172769151987771</v>
+        <v>-0.0074616429185198</v>
       </c>
       <c r="I4">
-        <v>0.3305197072389388</v>
+        <v>0.0712607498621743</v>
       </c>
       <c r="J4">
         <v>0.9</v>
@@ -767,22 +806,22 @@
         <v>141</v>
       </c>
       <c r="N4" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="O4" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="P4" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="Q4" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="R4" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="S4" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -790,25 +829,28 @@
         <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D5">
-        <v>0.0382743187697822</v>
+        <v>0.2011236993794083</v>
       </c>
       <c r="E5">
-        <v>0.0476145719195806</v>
+        <v>0.0786671870003106</v>
       </c>
       <c r="F5">
-        <v>0.4215846610455653</v>
+        <v>0.0106402549523447</v>
+      </c>
+      <c r="G5" t="s">
+        <v>62</v>
       </c>
       <c r="H5">
-        <v>-0.0400446825478817</v>
+        <v>0.07172769151987771</v>
       </c>
       <c r="I5">
-        <v>0.1165933200874463</v>
+        <v>0.3305197072389388</v>
       </c>
       <c r="J5">
         <v>0.9</v>
@@ -820,22 +862,22 @@
         <v>141</v>
       </c>
       <c r="N5" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="O5" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="P5" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="Q5" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="R5" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="S5" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -843,55 +885,55 @@
         <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D6">
-        <v>0.2031202350300649</v>
+        <v>0.1648343674131309</v>
       </c>
       <c r="E6">
-        <v>0.0911356848922763</v>
+        <v>0.0750669863006187</v>
       </c>
       <c r="F6">
-        <v>0.0259451075622649</v>
+        <v>0.0282156606181205</v>
       </c>
       <c r="G6" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="H6">
-        <v>0.0532153731902977</v>
+        <v>0.0413601627322416</v>
       </c>
       <c r="I6">
-        <v>0.3530250968698322</v>
+        <v>0.2883085720940202</v>
       </c>
       <c r="J6">
         <v>0.9</v>
       </c>
       <c r="K6">
-        <v>2075</v>
+        <v>2214</v>
       </c>
       <c r="L6">
         <v>141</v>
       </c>
       <c r="N6" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="O6" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="P6" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="Q6" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="R6" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="S6" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -899,52 +941,52 @@
         <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D7">
-        <v>0.034172700909818</v>
+        <v>0.0382743187697822</v>
       </c>
       <c r="E7">
-        <v>0.0591430903437533</v>
+        <v>0.0476145719195806</v>
       </c>
       <c r="F7">
-        <v>0.5634691379184456</v>
+        <v>0.4215846610455653</v>
       </c>
       <c r="H7">
-        <v>-0.0631090257512233</v>
+        <v>-0.0400446825478817</v>
       </c>
       <c r="I7">
-        <v>0.1314544275708593</v>
+        <v>0.1165933200874463</v>
       </c>
       <c r="J7">
         <v>0.9</v>
       </c>
       <c r="K7">
-        <v>2075</v>
+        <v>2214</v>
       </c>
       <c r="L7">
         <v>141</v>
       </c>
       <c r="N7" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="O7" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="P7" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="Q7" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="R7" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="S7" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -952,55 +994,55 @@
         <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D8">
-        <v>0.2072364021401371</v>
+        <v>0.2031202350300649</v>
       </c>
       <c r="E8">
-        <v>0.1162719669886714</v>
+        <v>0.0911356848922763</v>
       </c>
       <c r="F8">
-        <v>0.0748785547143722</v>
+        <v>0.0259451075622649</v>
       </c>
       <c r="G8" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="H8">
-        <v>0.0159860355260391</v>
+        <v>0.0532153731902977</v>
       </c>
       <c r="I8">
-        <v>0.3984867687542351</v>
+        <v>0.3530250968698322</v>
       </c>
       <c r="J8">
         <v>0.9</v>
       </c>
       <c r="K8">
-        <v>1797</v>
+        <v>2075</v>
       </c>
       <c r="L8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N8" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="O8" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="P8" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="Q8" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="R8" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="S8" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -1008,52 +1050,55 @@
         <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D9">
-        <v>0.0564664958691171</v>
+        <v>0.1534291170039864</v>
       </c>
       <c r="E9">
-        <v>0.0769850133595632</v>
+        <v>0.0898440719971855</v>
       </c>
       <c r="F9">
-        <v>0.4633743549062654</v>
+        <v>0.08784923753876871</v>
+      </c>
+      <c r="G9" t="s">
+        <v>63</v>
       </c>
       <c r="H9">
-        <v>-0.0701625825762679</v>
+        <v>0.0056487693193266</v>
       </c>
       <c r="I9">
-        <v>0.1830955743145023</v>
+        <v>0.3012094646886463</v>
       </c>
       <c r="J9">
         <v>0.9</v>
       </c>
       <c r="K9">
-        <v>1797</v>
+        <v>2075</v>
       </c>
       <c r="L9">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N9" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="O9" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="P9" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="Q9" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="R9" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="S9" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -1061,55 +1106,52 @@
         <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D10">
-        <v>0.2154708583914855</v>
+        <v>0.034172700909818</v>
       </c>
       <c r="E10">
-        <v>0.0889473323335303</v>
+        <v>0.0591430903437533</v>
       </c>
       <c r="F10">
-        <v>0.0155021492672606</v>
-      </c>
-      <c r="G10" t="s">
-        <v>48</v>
+        <v>0.5634691379184456</v>
       </c>
       <c r="H10">
-        <v>0.0691655161950202</v>
+        <v>-0.0631090257512233</v>
       </c>
       <c r="I10">
-        <v>0.3617762005879508</v>
+        <v>0.1314544275708593</v>
       </c>
       <c r="J10">
         <v>0.9</v>
       </c>
       <c r="K10">
-        <v>2214</v>
+        <v>2075</v>
       </c>
       <c r="L10">
         <v>141</v>
       </c>
       <c r="N10" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="O10" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="P10" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="Q10" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="R10" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="S10" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -1117,52 +1159,55 @@
         <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D11">
-        <v>-0.0850487429787847</v>
+        <v>0.2072364021401371</v>
       </c>
       <c r="E11">
-        <v>0.1336398123354226</v>
+        <v>0.1162719669886714</v>
       </c>
       <c r="F11">
-        <v>0.5245849332801513</v>
+        <v>0.0748785547143722</v>
+      </c>
+      <c r="G11" t="s">
+        <v>63</v>
       </c>
       <c r="H11">
-        <v>-0.3048666730038187</v>
+        <v>0.0159860355260391</v>
       </c>
       <c r="I11">
-        <v>0.1347691870462492</v>
+        <v>0.3984867687542351</v>
       </c>
       <c r="J11">
         <v>0.9</v>
       </c>
       <c r="K11">
-        <v>2214</v>
+        <v>1797</v>
       </c>
       <c r="L11">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="N11" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="O11" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="P11" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="Q11" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="R11" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="S11" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1170,55 +1215,52 @@
         <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D12">
-        <v>0.2285087916131138</v>
+        <v>0.1747736644811562</v>
       </c>
       <c r="E12">
-        <v>0.0860154538338444</v>
+        <v>0.1159552051153282</v>
       </c>
       <c r="F12">
-        <v>0.007954422130128201</v>
-      </c>
-      <c r="G12" t="s">
-        <v>50</v>
+        <v>0.1319388980970346</v>
       </c>
       <c r="H12">
-        <v>0.0870259604006379</v>
+        <v>-0.0159556752166933</v>
       </c>
       <c r="I12">
-        <v>0.3699916228255898</v>
+        <v>0.3655030041790058</v>
       </c>
       <c r="J12">
         <v>0.9</v>
       </c>
       <c r="K12">
-        <v>2214</v>
+        <v>1797</v>
       </c>
       <c r="L12">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="N12" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="O12" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="P12" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="Q12" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="R12" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="S12" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -1226,52 +1268,52 @@
         <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D13">
-        <v>0.09130623975805589</v>
+        <v>0.0564664958691171</v>
       </c>
       <c r="E13">
-        <v>0.1224377836656256</v>
+        <v>0.0769850133595632</v>
       </c>
       <c r="F13">
-        <v>0.4559124365996427</v>
+        <v>0.4633743549062654</v>
       </c>
       <c r="H13">
-        <v>-0.1100859927802482</v>
+        <v>-0.0701625825762679</v>
       </c>
       <c r="I13">
-        <v>0.29269847229636</v>
+        <v>0.1830955743145023</v>
       </c>
       <c r="J13">
         <v>0.9</v>
       </c>
       <c r="K13">
-        <v>2214</v>
+        <v>1797</v>
       </c>
       <c r="L13">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="N13" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="O13" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="P13" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="Q13" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="R13" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="S13" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -1279,28 +1321,28 @@
         <v>31</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D14">
-        <v>0.2019054059065828</v>
+        <v>0.2154708583914855</v>
       </c>
       <c r="E14">
-        <v>0.1002677955064552</v>
+        <v>0.0889473323335303</v>
       </c>
       <c r="F14">
-        <v>0.0441753969838283</v>
+        <v>0.0155021492672606</v>
       </c>
       <c r="G14" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="H14">
-        <v>0.0369795588013613</v>
+        <v>0.0691655161950202</v>
       </c>
       <c r="I14">
-        <v>0.3668312530118043</v>
+        <v>0.3617762005879508</v>
       </c>
       <c r="J14">
         <v>0.9</v>
@@ -1312,22 +1354,22 @@
         <v>141</v>
       </c>
       <c r="N14" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="O14" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="P14" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="Q14" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="R14" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="S14" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -1335,25 +1377,25 @@
         <v>32</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D15">
-        <v>-0.0943181043156498</v>
+        <v>0.1029762726623202</v>
       </c>
       <c r="E15">
-        <v>0.1270450668405377</v>
+        <v>0.1200495340442946</v>
       </c>
       <c r="F15">
-        <v>0.4579307216164767</v>
+        <v>0.391113285863008</v>
       </c>
       <c r="H15">
-        <v>-0.3032886432946006</v>
+        <v>-0.094487638824272</v>
       </c>
       <c r="I15">
-        <v>0.1146524346633008</v>
+        <v>0.3004401841489126</v>
       </c>
       <c r="J15">
         <v>0.9</v>
@@ -1365,22 +1407,405 @@
         <v>141</v>
       </c>
       <c r="N15" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="O15" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="P15" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="Q15" t="s">
+        <v>72</v>
+      </c>
+      <c r="R15" t="s">
+        <v>79</v>
+      </c>
+      <c r="S15" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19">
+      <c r="A16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16">
+        <v>-0.0850487429787847</v>
+      </c>
+      <c r="E16">
+        <v>0.1336398123354226</v>
+      </c>
+      <c r="F16">
+        <v>0.5245849332801513</v>
+      </c>
+      <c r="H16">
+        <v>-0.3048666730038187</v>
+      </c>
+      <c r="I16">
+        <v>0.1347691870462492</v>
+      </c>
+      <c r="J16">
+        <v>0.9</v>
+      </c>
+      <c r="K16">
+        <v>2214</v>
+      </c>
+      <c r="L16">
+        <v>141</v>
+      </c>
+      <c r="N16" t="s">
+        <v>65</v>
+      </c>
+      <c r="O16" t="s">
+        <v>66</v>
+      </c>
+      <c r="P16" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>72</v>
+      </c>
+      <c r="R16" t="s">
+        <v>79</v>
+      </c>
+      <c r="S16" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19">
+      <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17">
+        <v>0.2285087916131138</v>
+      </c>
+      <c r="E17">
+        <v>0.0860154538338444</v>
+      </c>
+      <c r="F17">
+        <v>0.007954422130128201</v>
+      </c>
+      <c r="G17" t="s">
+        <v>64</v>
+      </c>
+      <c r="H17">
+        <v>0.0870259604006379</v>
+      </c>
+      <c r="I17">
+        <v>0.3699916228255898</v>
+      </c>
+      <c r="J17">
+        <v>0.9</v>
+      </c>
+      <c r="K17">
+        <v>2214</v>
+      </c>
+      <c r="L17">
+        <v>141</v>
+      </c>
+      <c r="N17" t="s">
+        <v>65</v>
+      </c>
+      <c r="O17" t="s">
+        <v>66</v>
+      </c>
+      <c r="P17" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>73</v>
+      </c>
+      <c r="R17" t="s">
+        <v>80</v>
+      </c>
+      <c r="S17" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
+      <c r="A18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18">
+        <v>0.2264419842643394</v>
+      </c>
+      <c r="E18">
+        <v>0.1162684701053057</v>
+      </c>
+      <c r="F18">
+        <v>0.0516016239637981</v>
+      </c>
+      <c r="G18" t="s">
+        <v>63</v>
+      </c>
+      <c r="H18">
+        <v>0.0351973695115284</v>
+      </c>
+      <c r="I18">
+        <v>0.4176865990171503</v>
+      </c>
+      <c r="J18">
+        <v>0.9</v>
+      </c>
+      <c r="K18">
+        <v>2214</v>
+      </c>
+      <c r="L18">
+        <v>141</v>
+      </c>
+      <c r="N18" t="s">
+        <v>65</v>
+      </c>
+      <c r="O18" t="s">
+        <v>66</v>
+      </c>
+      <c r="P18" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>73</v>
+      </c>
+      <c r="R18" t="s">
+        <v>80</v>
+      </c>
+      <c r="S18" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
+      <c r="A19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19">
+        <v>0.09130623975805589</v>
+      </c>
+      <c r="E19">
+        <v>0.1224377836656256</v>
+      </c>
+      <c r="F19">
+        <v>0.4559124365996427</v>
+      </c>
+      <c r="H19">
+        <v>-0.1100859927802482</v>
+      </c>
+      <c r="I19">
+        <v>0.29269847229636</v>
+      </c>
+      <c r="J19">
+        <v>0.9</v>
+      </c>
+      <c r="K19">
+        <v>2214</v>
+      </c>
+      <c r="L19">
+        <v>141</v>
+      </c>
+      <c r="N19" t="s">
+        <v>65</v>
+      </c>
+      <c r="O19" t="s">
+        <v>66</v>
+      </c>
+      <c r="P19" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>73</v>
+      </c>
+      <c r="R19" t="s">
+        <v>80</v>
+      </c>
+      <c r="S19" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19">
+      <c r="A20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20">
+        <v>0.2019054059065828</v>
+      </c>
+      <c r="E20">
+        <v>0.1002677955064552</v>
+      </c>
+      <c r="F20">
+        <v>0.0441753969838283</v>
+      </c>
+      <c r="G20" t="s">
+        <v>62</v>
+      </c>
+      <c r="H20">
+        <v>0.0369795588013613</v>
+      </c>
+      <c r="I20">
+        <v>0.3668312530118043</v>
+      </c>
+      <c r="J20">
+        <v>0.9</v>
+      </c>
+      <c r="K20">
+        <v>2214</v>
+      </c>
+      <c r="L20">
+        <v>141</v>
+      </c>
+      <c r="N20" t="s">
+        <v>65</v>
+      </c>
+      <c r="O20" t="s">
+        <v>66</v>
+      </c>
+      <c r="P20" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>74</v>
+      </c>
+      <c r="R20" t="s">
+        <v>81</v>
+      </c>
+      <c r="S20" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19">
+      <c r="A21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" t="s">
         <v>60</v>
       </c>
-      <c r="R15" t="s">
-        <v>67</v>
-      </c>
-      <c r="S15" t="s">
-        <v>70</v>
+      <c r="D21">
+        <v>0.2958377047243033</v>
+      </c>
+      <c r="E21">
+        <v>0.09758071794449411</v>
+      </c>
+      <c r="F21">
+        <v>0.0024620459118562</v>
+      </c>
+      <c r="G21" t="s">
+        <v>64</v>
+      </c>
+      <c r="H21">
+        <v>0.1353317068927735</v>
+      </c>
+      <c r="I21">
+        <v>0.4563437025558331</v>
+      </c>
+      <c r="J21">
+        <v>0.9</v>
+      </c>
+      <c r="K21">
+        <v>2214</v>
+      </c>
+      <c r="L21">
+        <v>141</v>
+      </c>
+      <c r="N21" t="s">
+        <v>65</v>
+      </c>
+      <c r="O21" t="s">
+        <v>66</v>
+      </c>
+      <c r="P21" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>74</v>
+      </c>
+      <c r="R21" t="s">
+        <v>81</v>
+      </c>
+      <c r="S21" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19">
+      <c r="A22" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22">
+        <v>-0.0943181043156498</v>
+      </c>
+      <c r="E22">
+        <v>0.1270450668405377</v>
+      </c>
+      <c r="F22">
+        <v>0.4579307216164767</v>
+      </c>
+      <c r="H22">
+        <v>-0.3032886432946006</v>
+      </c>
+      <c r="I22">
+        <v>0.1146524346633008</v>
+      </c>
+      <c r="J22">
+        <v>0.9</v>
+      </c>
+      <c r="K22">
+        <v>2214</v>
+      </c>
+      <c r="L22">
+        <v>141</v>
+      </c>
+      <c r="N22" t="s">
+        <v>65</v>
+      </c>
+      <c r="O22" t="s">
+        <v>66</v>
+      </c>
+      <c r="P22" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>74</v>
+      </c>
+      <c r="R22" t="s">
+        <v>81</v>
+      </c>
+      <c r="S22" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
